--- a/BX/IRR and SI/templates/提取模板.xlsx
+++ b/BX/IRR and SI/templates/提取模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-21AJPF46TWSF-Data\chenwang\Desktop\my cursor\BX\IRR and SI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD64D96-9819-411F-AD42-470BDC01F8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7689D1D6-D2D4-4D40-AD63-6506F0DA0DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="储蓄利益演示" sheetId="1" r:id="rId1"/>
@@ -22,1063 +22,703 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
   <si>
-    <t>1年/1歲</t>
-  </si>
-  <si>
     <t>6,800</t>
   </si>
   <si>
-    <t>2年/2歲</t>
-  </si>
-  <si>
     <t>18,606</t>
   </si>
   <si>
-    <t>3年/3歲</t>
-  </si>
-  <si>
     <t>82,419</t>
   </si>
   <si>
-    <t>4年/4歲</t>
-  </si>
-  <si>
     <t>178,295</t>
   </si>
   <si>
-    <t>5年/5歲</t>
-  </si>
-  <si>
     <t>311,613</t>
   </si>
   <si>
-    <t>6年/6歲</t>
-  </si>
-  <si>
     <t>70,000</t>
   </si>
   <si>
     <t>547,323</t>
   </si>
   <si>
-    <t>7年/7歲</t>
-  </si>
-  <si>
     <t>140,000</t>
   </si>
   <si>
     <t>899,581</t>
   </si>
   <si>
-    <t>8年/8歲</t>
-  </si>
-  <si>
     <t>210,000</t>
   </si>
   <si>
     <t>905,450</t>
   </si>
   <si>
-    <t>9年/9歲</t>
-  </si>
-  <si>
     <t>280,000</t>
   </si>
   <si>
     <t>904,172</t>
   </si>
   <si>
-    <t>10年/10歲</t>
-  </si>
-  <si>
     <t>350,000</t>
   </si>
   <si>
     <t>912,156</t>
   </si>
   <si>
-    <t>11年/11歲</t>
-  </si>
-  <si>
     <t>420,000</t>
   </si>
   <si>
     <t>864,767</t>
   </si>
   <si>
-    <t>12年/12歲</t>
-  </si>
-  <si>
     <t>490,000</t>
   </si>
   <si>
     <t>824,953</t>
   </si>
   <si>
-    <t>13年/13歲</t>
-  </si>
-  <si>
     <t>560,000</t>
   </si>
   <si>
     <t>981,668</t>
   </si>
   <si>
-    <t>14年/14歲</t>
-  </si>
-  <si>
     <t>630,000</t>
   </si>
   <si>
     <t>976,128</t>
   </si>
   <si>
-    <t>15年/15歲</t>
-  </si>
-  <si>
     <t>700,000</t>
   </si>
   <si>
     <t>983,848</t>
   </si>
   <si>
-    <t>16年/16歲</t>
-  </si>
-  <si>
     <t>770,000</t>
   </si>
   <si>
     <t>1,002,691</t>
   </si>
   <si>
-    <t>17年/17歲</t>
-  </si>
-  <si>
     <t>840,000</t>
   </si>
   <si>
     <t>1,008,510</t>
   </si>
   <si>
-    <t>18年/18歲</t>
-  </si>
-  <si>
     <t>910,000</t>
   </si>
   <si>
     <t>1,027,999</t>
   </si>
   <si>
-    <t>19年/19歲</t>
-  </si>
-  <si>
     <t>980,000</t>
   </si>
   <si>
     <t>1,053,663</t>
   </si>
   <si>
-    <t>20年/20歲</t>
-  </si>
-  <si>
     <t>1,050,000</t>
   </si>
   <si>
     <t>1,118,586</t>
   </si>
   <si>
-    <t>21年/21歲</t>
-  </si>
-  <si>
     <t>1,120,000</t>
   </si>
   <si>
     <t>1,137,343</t>
   </si>
   <si>
-    <t>22年/22歲</t>
-  </si>
-  <si>
     <t>1,190,000</t>
   </si>
   <si>
     <t>1,159,806</t>
   </si>
   <si>
-    <t>23年/23歲</t>
-  </si>
-  <si>
     <t>1,260,000</t>
   </si>
   <si>
     <t>1,184,404</t>
   </si>
   <si>
-    <t>24年/24歲</t>
-  </si>
-  <si>
     <t>1,330,000</t>
   </si>
   <si>
     <t>1,212,321</t>
   </si>
   <si>
-    <t>25年/25歲</t>
-  </si>
-  <si>
     <t>1,400,000</t>
   </si>
   <si>
     <t>1,246,384</t>
   </si>
   <si>
-    <t>26年/26歲</t>
-  </si>
-  <si>
     <t>1,470,000</t>
   </si>
   <si>
     <t>1,273,856</t>
   </si>
   <si>
-    <t>27年/27歲</t>
-  </si>
-  <si>
     <t>1,540,000</t>
   </si>
   <si>
     <t>1,318,595</t>
   </si>
   <si>
-    <t>28年/28歲</t>
-  </si>
-  <si>
     <t>1,610,000</t>
   </si>
   <si>
     <t>1,344,861</t>
   </si>
   <si>
-    <t>29年/29歲</t>
-  </si>
-  <si>
     <t>1,680,000</t>
   </si>
   <si>
     <t>1,376,694</t>
   </si>
   <si>
-    <t>30年/30歲</t>
-  </si>
-  <si>
     <t>1,750,000</t>
   </si>
   <si>
     <t>1,487,169</t>
   </si>
   <si>
-    <t>31年/31歲</t>
-  </si>
-  <si>
     <t>1,820,000</t>
   </si>
   <si>
     <t>1,523,533</t>
   </si>
   <si>
-    <t>32年/32歲</t>
-  </si>
-  <si>
     <t>1,890,000</t>
   </si>
   <si>
     <t>1,567,457</t>
   </si>
   <si>
-    <t>33年/33歲</t>
-  </si>
-  <si>
     <t>1,960,000</t>
   </si>
   <si>
     <t>1,613,785</t>
   </si>
   <si>
-    <t>34年/34歲</t>
-  </si>
-  <si>
     <t>2,030,000</t>
   </si>
   <si>
     <t>1,664,319</t>
   </si>
   <si>
-    <t>35年/35歲</t>
-  </si>
-  <si>
     <t>2,100,000</t>
   </si>
   <si>
     <t>1,718,477</t>
   </si>
   <si>
-    <t>36年/36歲</t>
-  </si>
-  <si>
     <t>2,170,000</t>
   </si>
   <si>
     <t>1,776,694</t>
   </si>
   <si>
-    <t>37年/37歲</t>
-  </si>
-  <si>
     <t>2,240,000</t>
   </si>
   <si>
     <t>1,838,338</t>
   </si>
   <si>
-    <t>38年/38歲</t>
-  </si>
-  <si>
     <t>2,310,000</t>
   </si>
   <si>
     <t>1,905,365</t>
   </si>
   <si>
-    <t>39年/39歲</t>
-  </si>
-  <si>
     <t>2,380,000</t>
   </si>
   <si>
     <t>1,977,293</t>
   </si>
   <si>
-    <t>40年/40歲</t>
-  </si>
-  <si>
     <t>2,450,000</t>
   </si>
   <si>
     <t>2,054,493</t>
   </si>
   <si>
-    <t>41年/41歲</t>
-  </si>
-  <si>
     <t>2,520,000</t>
   </si>
   <si>
     <t>2,137,352</t>
   </si>
   <si>
-    <t>42年/42歲</t>
-  </si>
-  <si>
     <t>2,590,000</t>
   </si>
   <si>
     <t>2,225,479</t>
   </si>
   <si>
-    <t>43年/43歲</t>
-  </si>
-  <si>
     <t>2,660,000</t>
   </si>
   <si>
     <t>2,320,955</t>
   </si>
   <si>
-    <t>44年/44歲</t>
-  </si>
-  <si>
     <t>2,730,000</t>
   </si>
   <si>
     <t>2,423,459</t>
   </si>
   <si>
-    <t>45年/45歲</t>
-  </si>
-  <si>
     <t>2,800,000</t>
   </si>
   <si>
     <t>2,533,520</t>
   </si>
   <si>
-    <t>46年/46歲</t>
-  </si>
-  <si>
     <t>2,870,000</t>
   </si>
   <si>
     <t>2,652,062</t>
   </si>
   <si>
-    <t>47年/47歲</t>
-  </si>
-  <si>
     <t>2,940,000</t>
   </si>
   <si>
     <t>2,778,492</t>
   </si>
   <si>
-    <t>48年/48歲</t>
-  </si>
-  <si>
     <t>3,010,000</t>
   </si>
   <si>
     <t>2,915,303</t>
   </si>
   <si>
-    <t>49年/49歲</t>
-  </si>
-  <si>
     <t>3,080,000</t>
   </si>
   <si>
     <t>3,059,867</t>
   </si>
   <si>
-    <t>50年/50歲</t>
-  </si>
-  <si>
     <t>3,150,000</t>
   </si>
   <si>
     <t>3,218,512</t>
   </si>
   <si>
-    <t>51年/51歲</t>
-  </si>
-  <si>
     <t>3,220,000</t>
   </si>
   <si>
     <t>3,370,669</t>
   </si>
   <si>
-    <t>52年/52歲</t>
-  </si>
-  <si>
     <t>3,290,000</t>
   </si>
   <si>
     <t>3,532,776</t>
   </si>
   <si>
-    <t>53年/53歲</t>
-  </si>
-  <si>
     <t>3,360,000</t>
   </si>
   <si>
     <t>3,705,486</t>
   </si>
   <si>
-    <t>54年/54歲</t>
-  </si>
-  <si>
     <t>3,430,000</t>
   </si>
   <si>
     <t>3,889,495</t>
   </si>
   <si>
-    <t>55年/55歲</t>
-  </si>
-  <si>
     <t>3,500,000</t>
   </si>
   <si>
     <t>4,085,544</t>
   </si>
   <si>
-    <t>56年/56歲</t>
-  </si>
-  <si>
     <t>3,570,000</t>
   </si>
   <si>
     <t>4,294,422</t>
   </si>
   <si>
-    <t>57年/57歲</t>
-  </si>
-  <si>
     <t>3,640,000</t>
   </si>
   <si>
     <t>4,516,969</t>
   </si>
   <si>
-    <t>58年/58歲</t>
-  </si>
-  <si>
     <t>3,710,000</t>
   </si>
   <si>
     <t>4,754,081</t>
   </si>
   <si>
-    <t>59年/59歲</t>
-  </si>
-  <si>
     <t>3,780,000</t>
   </si>
   <si>
     <t>5,006,710</t>
   </si>
   <si>
-    <t>60年/60歲</t>
-  </si>
-  <si>
     <t>3,850,000</t>
   </si>
   <si>
     <t>5,274,125</t>
   </si>
   <si>
-    <t>61年/61歲</t>
-  </si>
-  <si>
     <t>3,920,000</t>
   </si>
   <si>
     <t>5,560,885</t>
   </si>
   <si>
-    <t>62年/62歲</t>
-  </si>
-  <si>
     <t>3,990,000</t>
   </si>
   <si>
     <t>5,866,409</t>
   </si>
   <si>
-    <t>63年/63歲</t>
-  </si>
-  <si>
     <t>4,060,000</t>
   </si>
   <si>
     <t>6,191,923</t>
   </si>
   <si>
-    <t>64年/64歲</t>
-  </si>
-  <si>
     <t>4,130,000</t>
   </si>
   <si>
     <t>6,538,732</t>
   </si>
   <si>
-    <t>65年/65歲</t>
-  </si>
-  <si>
     <t>4,200,000</t>
   </si>
   <si>
     <t>6,908,226</t>
   </si>
   <si>
-    <t>66年/66歲</t>
-  </si>
-  <si>
     <t>4,270,000</t>
   </si>
   <si>
     <t>7,301,885</t>
   </si>
   <si>
-    <t>67年/67歲</t>
-  </si>
-  <si>
     <t>4,340,000</t>
   </si>
   <si>
     <t>7,721,285</t>
   </si>
   <si>
-    <t>68年/68歲</t>
-  </si>
-  <si>
     <t>4,410,000</t>
   </si>
   <si>
     <t>8,168,107</t>
   </si>
   <si>
-    <t>69年/69歲</t>
-  </si>
-  <si>
     <t>4,480,000</t>
   </si>
   <si>
     <t>8,644,136</t>
   </si>
   <si>
-    <t>70年/70歲</t>
-  </si>
-  <si>
     <t>4,550,000</t>
   </si>
   <si>
     <t>9,151,277</t>
   </si>
   <si>
-    <t>71年/71歲</t>
-  </si>
-  <si>
     <t>4,620,000</t>
   </si>
   <si>
     <t>9,691,559</t>
   </si>
   <si>
-    <t>72年/72歲</t>
-  </si>
-  <si>
     <t>4,690,000</t>
   </si>
   <si>
     <t>10,267,140</t>
   </si>
   <si>
-    <t>73年/73歲</t>
-  </si>
-  <si>
     <t>4,760,000</t>
   </si>
   <si>
     <t>10,880,320</t>
   </si>
   <si>
-    <t>74年/74歲</t>
-  </si>
-  <si>
     <t>4,830,000</t>
   </si>
   <si>
     <t>11,533,547</t>
   </si>
   <si>
-    <t>75年/75歲</t>
-  </si>
-  <si>
     <t>4,900,000</t>
   </si>
   <si>
     <t>12,229,430</t>
   </si>
   <si>
-    <t>76年/76歲</t>
-  </si>
-  <si>
     <t>4,970,000</t>
   </si>
   <si>
     <t>12,956,301</t>
   </si>
   <si>
-    <t>77年/77歲</t>
-  </si>
-  <si>
     <t>5,040,000</t>
   </si>
   <si>
     <t>13,728,461</t>
   </si>
   <si>
-    <t>78年/78歲</t>
-  </si>
-  <si>
     <t>5,110,000</t>
   </si>
   <si>
     <t>14,550,811</t>
   </si>
   <si>
-    <t>79年/79歲</t>
-  </si>
-  <si>
     <t>5,180,000</t>
   </si>
   <si>
     <t>15,426,614</t>
   </si>
   <si>
-    <t>80年/80歲</t>
-  </si>
-  <si>
     <t>5,250,000</t>
   </si>
   <si>
     <t>16,359,344</t>
   </si>
   <si>
-    <t>81年/81歲</t>
-  </si>
-  <si>
     <t>5,320,000</t>
   </si>
   <si>
     <t>17,352,701</t>
   </si>
   <si>
-    <t>82年/82歲</t>
-  </si>
-  <si>
     <t>5,390,000</t>
   </si>
   <si>
     <t>18,410,627</t>
   </si>
   <si>
-    <t>83年/83歲</t>
-  </si>
-  <si>
     <t>5,460,000</t>
   </si>
   <si>
     <t>19,537,317</t>
   </si>
   <si>
-    <t>84年/84歲</t>
-  </si>
-  <si>
     <t>5,530,000</t>
   </si>
   <si>
     <t>20,737,243</t>
   </si>
   <si>
-    <t>85年/85歲</t>
-  </si>
-  <si>
     <t>5,600,000</t>
   </si>
   <si>
     <t>22,015,164</t>
   </si>
   <si>
-    <t>86年/86歲</t>
-  </si>
-  <si>
     <t>5,670,000</t>
   </si>
   <si>
     <t>23,376,149</t>
   </si>
   <si>
-    <t>87年/87歲</t>
-  </si>
-  <si>
     <t>5,740,000</t>
   </si>
   <si>
     <t>24,825,599</t>
   </si>
   <si>
-    <t>88年/88歲</t>
-  </si>
-  <si>
     <t>5,810,000</t>
   </si>
   <si>
     <t>26,369,263</t>
   </si>
   <si>
-    <t>89年/89歲</t>
-  </si>
-  <si>
     <t>5,880,000</t>
   </si>
   <si>
     <t>28,013,265</t>
   </si>
   <si>
-    <t>90年/90歲</t>
-  </si>
-  <si>
     <t>5,950,000</t>
   </si>
   <si>
     <t>29,764,127</t>
   </si>
   <si>
-    <t>91年/91歲</t>
-  </si>
-  <si>
     <t>6,020,000</t>
   </si>
   <si>
     <t>31,628,795</t>
   </si>
   <si>
-    <t>92年/92歲</t>
-  </si>
-  <si>
     <t>6,090,000</t>
   </si>
   <si>
     <t>33,614,667</t>
   </si>
   <si>
-    <t>93年/93歲</t>
-  </si>
-  <si>
     <t>6,160,000</t>
   </si>
   <si>
     <t>35,729,621</t>
   </si>
   <si>
-    <t>94年/94歲</t>
-  </si>
-  <si>
     <t>6,230,000</t>
   </si>
   <si>
     <t>37,982,046</t>
   </si>
   <si>
-    <t>95年/95歲</t>
-  </si>
-  <si>
     <t>6,300,000</t>
   </si>
   <si>
     <t>40,380,879</t>
   </si>
   <si>
-    <t>96年/96歲</t>
-  </si>
-  <si>
     <t>6,370,000</t>
   </si>
   <si>
     <t>42,935,636</t>
   </si>
   <si>
-    <t>97年/97歲</t>
-  </si>
-  <si>
     <t>6,440,000</t>
   </si>
   <si>
     <t>45,656,452</t>
   </si>
   <si>
-    <t>98年/98歲</t>
-  </si>
-  <si>
     <t>6,510,000</t>
   </si>
   <si>
     <t>48,554,122</t>
   </si>
   <si>
-    <t>99年/99歲</t>
-  </si>
-  <si>
     <t>6,580,000</t>
   </si>
   <si>
     <t>51,640,140</t>
   </si>
   <si>
-    <t>100年/100歲</t>
-  </si>
-  <si>
     <t>6,650,000</t>
   </si>
   <si>
     <t>54,926,749</t>
   </si>
   <si>
-    <t>101年/101歲</t>
-  </si>
-  <si>
     <t>6,720,000</t>
   </si>
   <si>
     <t>58,426,987</t>
   </si>
   <si>
-    <t>102年/102歲</t>
-  </si>
-  <si>
     <t>6,790,000</t>
   </si>
   <si>
     <t>62,154,742</t>
   </si>
   <si>
-    <t>103年/103歲</t>
-  </si>
-  <si>
     <t>6,860,000</t>
   </si>
   <si>
     <t>66,124,800</t>
   </si>
   <si>
-    <t>104年/104歲</t>
-  </si>
-  <si>
     <t>6,930,000</t>
   </si>
   <si>
     <t>70,352,912</t>
   </si>
   <si>
-    <t>105年/105歲</t>
-  </si>
-  <si>
     <t>7,000,000</t>
   </si>
   <si>
     <t>74,855,851</t>
   </si>
   <si>
-    <t>106年/106歲</t>
-  </si>
-  <si>
     <t>7,070,000</t>
   </si>
   <si>
     <t>79,651,481</t>
   </si>
   <si>
-    <t>107年/107歲</t>
-  </si>
-  <si>
     <t>7,140,000</t>
   </si>
   <si>
     <t>84,758,828</t>
   </si>
   <si>
-    <t>108年/108歲</t>
-  </si>
-  <si>
     <t>7,210,000</t>
   </si>
   <si>
     <t>90,198,151</t>
   </si>
   <si>
-    <t>109年/109歲</t>
-  </si>
-  <si>
     <t>7,280,000</t>
   </si>
   <si>
     <t>95,991,031</t>
   </si>
   <si>
-    <t>110年/110歲</t>
-  </si>
-  <si>
     <t>7,350,000</t>
   </si>
   <si>
     <t>102,160,448</t>
   </si>
   <si>
-    <t>111年/111歲</t>
-  </si>
-  <si>
     <t>7,420,000</t>
   </si>
   <si>
     <t>108,730,877</t>
   </si>
   <si>
-    <t>112年/112歲</t>
-  </si>
-  <si>
     <t>7,490,000</t>
   </si>
   <si>
     <t>115,728,384</t>
   </si>
   <si>
-    <t>113年/113歲</t>
-  </si>
-  <si>
     <t>7,560,000</t>
   </si>
   <si>
     <t>123,180,729</t>
   </si>
   <si>
-    <t>114年/114歲</t>
-  </si>
-  <si>
     <t>7,630,000</t>
   </si>
   <si>
     <t>131,117,477</t>
   </si>
   <si>
-    <t>115年/115歲</t>
-  </si>
-  <si>
     <t>7,700,000</t>
   </si>
   <si>
     <t>139,570,113</t>
   </si>
   <si>
-    <t>116年/116歲</t>
-  </si>
-  <si>
     <t>7,770,000</t>
   </si>
   <si>
     <t>148,572,170</t>
   </si>
   <si>
-    <t>117年/117歲</t>
-  </si>
-  <si>
     <t>7,840,000</t>
   </si>
   <si>
     <t>158,159,361</t>
   </si>
   <si>
-    <t>118年/118歲</t>
-  </si>
-  <si>
     <t>7,910,000</t>
   </si>
   <si>
     <t>168,369,720</t>
   </si>
   <si>
-    <t>119年/119歲</t>
-  </si>
-  <si>
     <t>7,980,000</t>
   </si>
   <si>
     <t>179,243,752</t>
-  </si>
-  <si>
-    <t>120年/120歲</t>
   </si>
   <si>
     <t>8,050,000</t>
@@ -1126,6 +766,368 @@
       <t>列即可</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3年</t>
+  </si>
+  <si>
+    <t>4年</t>
+  </si>
+  <si>
+    <t>5年</t>
+  </si>
+  <si>
+    <t>6年</t>
+  </si>
+  <si>
+    <t>7年</t>
+  </si>
+  <si>
+    <t>8年</t>
+  </si>
+  <si>
+    <t>9年</t>
+  </si>
+  <si>
+    <t>10年</t>
+  </si>
+  <si>
+    <t>11年</t>
+  </si>
+  <si>
+    <t>12年</t>
+  </si>
+  <si>
+    <t>13年</t>
+  </si>
+  <si>
+    <t>14年</t>
+  </si>
+  <si>
+    <t>15年</t>
+  </si>
+  <si>
+    <t>16年</t>
+  </si>
+  <si>
+    <t>17年</t>
+  </si>
+  <si>
+    <t>18年</t>
+  </si>
+  <si>
+    <t>19年</t>
+  </si>
+  <si>
+    <t>20年</t>
+  </si>
+  <si>
+    <t>21年</t>
+  </si>
+  <si>
+    <t>22年</t>
+  </si>
+  <si>
+    <t>23年</t>
+  </si>
+  <si>
+    <t>24年</t>
+  </si>
+  <si>
+    <t>25年</t>
+  </si>
+  <si>
+    <t>26年</t>
+  </si>
+  <si>
+    <t>27年</t>
+  </si>
+  <si>
+    <t>28年</t>
+  </si>
+  <si>
+    <t>29年</t>
+  </si>
+  <si>
+    <t>30年</t>
+  </si>
+  <si>
+    <t>31年</t>
+  </si>
+  <si>
+    <t>32年</t>
+  </si>
+  <si>
+    <t>33年</t>
+  </si>
+  <si>
+    <t>34年</t>
+  </si>
+  <si>
+    <t>35年</t>
+  </si>
+  <si>
+    <t>36年</t>
+  </si>
+  <si>
+    <t>37年</t>
+  </si>
+  <si>
+    <t>38年</t>
+  </si>
+  <si>
+    <t>39年</t>
+  </si>
+  <si>
+    <t>40年</t>
+  </si>
+  <si>
+    <t>41年</t>
+  </si>
+  <si>
+    <t>42年</t>
+  </si>
+  <si>
+    <t>43年</t>
+  </si>
+  <si>
+    <t>44年</t>
+  </si>
+  <si>
+    <t>45年</t>
+  </si>
+  <si>
+    <t>46年</t>
+  </si>
+  <si>
+    <t>47年</t>
+  </si>
+  <si>
+    <t>48年</t>
+  </si>
+  <si>
+    <t>49年</t>
+  </si>
+  <si>
+    <t>50年</t>
+  </si>
+  <si>
+    <t>51年</t>
+  </si>
+  <si>
+    <t>52年</t>
+  </si>
+  <si>
+    <t>53年</t>
+  </si>
+  <si>
+    <t>54年</t>
+  </si>
+  <si>
+    <t>55年</t>
+  </si>
+  <si>
+    <t>56年</t>
+  </si>
+  <si>
+    <t>57年</t>
+  </si>
+  <si>
+    <t>58年</t>
+  </si>
+  <si>
+    <t>59年</t>
+  </si>
+  <si>
+    <t>60年</t>
+  </si>
+  <si>
+    <t>61年</t>
+  </si>
+  <si>
+    <t>62年</t>
+  </si>
+  <si>
+    <t>63年</t>
+  </si>
+  <si>
+    <t>64年</t>
+  </si>
+  <si>
+    <t>65年</t>
+  </si>
+  <si>
+    <t>66年</t>
+  </si>
+  <si>
+    <t>67年</t>
+  </si>
+  <si>
+    <t>68年</t>
+  </si>
+  <si>
+    <t>69年</t>
+  </si>
+  <si>
+    <t>70年</t>
+  </si>
+  <si>
+    <t>71年</t>
+  </si>
+  <si>
+    <t>72年</t>
+  </si>
+  <si>
+    <t>73年</t>
+  </si>
+  <si>
+    <t>74年</t>
+  </si>
+  <si>
+    <t>75年</t>
+  </si>
+  <si>
+    <t>76年</t>
+  </si>
+  <si>
+    <t>77年</t>
+  </si>
+  <si>
+    <t>78年</t>
+  </si>
+  <si>
+    <t>79年</t>
+  </si>
+  <si>
+    <t>80年</t>
+  </si>
+  <si>
+    <t>81年</t>
+  </si>
+  <si>
+    <t>82年</t>
+  </si>
+  <si>
+    <t>83年</t>
+  </si>
+  <si>
+    <t>84年</t>
+  </si>
+  <si>
+    <t>85年</t>
+  </si>
+  <si>
+    <t>86年</t>
+  </si>
+  <si>
+    <t>87年</t>
+  </si>
+  <si>
+    <t>88年</t>
+  </si>
+  <si>
+    <t>89年</t>
+  </si>
+  <si>
+    <t>90年</t>
+  </si>
+  <si>
+    <t>91年</t>
+  </si>
+  <si>
+    <t>92年</t>
+  </si>
+  <si>
+    <t>93年</t>
+  </si>
+  <si>
+    <t>94年</t>
+  </si>
+  <si>
+    <t>95年</t>
+  </si>
+  <si>
+    <t>96年</t>
+  </si>
+  <si>
+    <t>97年</t>
+  </si>
+  <si>
+    <t>98年</t>
+  </si>
+  <si>
+    <t>99年</t>
+  </si>
+  <si>
+    <t>100年</t>
+  </si>
+  <si>
+    <t>101年</t>
+  </si>
+  <si>
+    <t>102年</t>
+  </si>
+  <si>
+    <t>103年</t>
+  </si>
+  <si>
+    <t>104年</t>
+  </si>
+  <si>
+    <t>105年</t>
+  </si>
+  <si>
+    <t>106年</t>
+  </si>
+  <si>
+    <t>107年</t>
+  </si>
+  <si>
+    <t>108年</t>
+  </si>
+  <si>
+    <t>109年</t>
+  </si>
+  <si>
+    <t>110年</t>
+  </si>
+  <si>
+    <t>111年</t>
+  </si>
+  <si>
+    <t>112年</t>
+  </si>
+  <si>
+    <t>113年</t>
+  </si>
+  <si>
+    <t>114年</t>
+  </si>
+  <si>
+    <t>115年</t>
+  </si>
+  <si>
+    <t>116年</t>
+  </si>
+  <si>
+    <t>117年</t>
+  </si>
+  <si>
+    <t>118年</t>
+  </si>
+  <si>
+    <t>119年</t>
+  </si>
+  <si>
+    <t>120年</t>
   </si>
 </sst>
 </file>
@@ -1281,13 +1283,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1629,8 +1631,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K128"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K122"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="14.25" customWidth="1"/>
     <col min="4" max="5" width="20.25" customWidth="1"/>
@@ -1641,23 +1643,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
+      <c r="A1" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>235</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
@@ -1665,18 +1667,18 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>356</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="3" t="s">
-        <v>357</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1688,12 +1690,12 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1705,12 +1707,12 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>241</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1722,12 +1724,12 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>242</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1739,12 +1741,12 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>243</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1756,12 +1758,12 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1769,18 +1771,18 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>245</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1788,18 +1790,18 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1807,18 +1809,18 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>247</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1826,18 +1828,18 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>248</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1845,18 +1847,18 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>249</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1864,18 +1866,18 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1883,18 +1885,18 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>251</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1902,18 +1904,18 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1921,18 +1923,18 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>37</v>
+      <c r="A17" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1940,18 +1942,18 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>40</v>
+      <c r="A18" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1959,18 +1961,18 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>43</v>
+      <c r="A19" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1978,18 +1980,18 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
+      <c r="A20" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1997,18 +1999,18 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>49</v>
+      <c r="A21" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2016,18 +2018,18 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>52</v>
+      <c r="A22" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2035,18 +2037,18 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>55</v>
+      <c r="A23" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2054,18 +2056,18 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>58</v>
+      <c r="A24" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2073,18 +2075,18 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>61</v>
+      <c r="A25" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2092,18 +2094,18 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>64</v>
+      <c r="A26" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2111,18 +2113,18 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>67</v>
+      <c r="A27" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2130,18 +2132,18 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>70</v>
+      <c r="A28" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2149,18 +2151,18 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>73</v>
+      <c r="A29" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2168,18 +2170,18 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>76</v>
+      <c r="A30" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2187,18 +2189,18 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>79</v>
+      <c r="A31" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2206,18 +2208,18 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>82</v>
+      <c r="A32" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2225,18 +2227,18 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>85</v>
+      <c r="A33" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2244,18 +2246,18 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>88</v>
+      <c r="A34" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2263,18 +2265,18 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>91</v>
+      <c r="A35" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2282,18 +2284,18 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>94</v>
+      <c r="A36" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2301,18 +2303,18 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>97</v>
+      <c r="A37" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2320,18 +2322,18 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>100</v>
+      <c r="A38" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2339,18 +2341,18 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>103</v>
+      <c r="A39" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2358,18 +2360,18 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>106</v>
+      <c r="A40" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2377,18 +2379,18 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>109</v>
+      <c r="A41" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2396,18 +2398,18 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>112</v>
+      <c r="A42" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2415,18 +2417,18 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>115</v>
+      <c r="A43" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2434,18 +2436,18 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>118</v>
+      <c r="A44" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2453,18 +2455,18 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>121</v>
+      <c r="A45" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2472,18 +2474,18 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>124</v>
+      <c r="A46" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2491,18 +2493,18 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>127</v>
+      <c r="A47" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2510,18 +2512,18 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>130</v>
+      <c r="A48" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2529,18 +2531,18 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
-        <v>133</v>
+      <c r="A49" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2548,18 +2550,18 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>136</v>
+      <c r="A50" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2567,18 +2569,18 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>139</v>
+      <c r="A51" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2586,18 +2588,18 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>142</v>
+      <c r="A52" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2605,18 +2607,18 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>145</v>
+      <c r="A53" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2624,18 +2626,18 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
-        <v>148</v>
+      <c r="A54" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2643,18 +2645,18 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
-        <v>151</v>
+      <c r="A55" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2662,18 +2664,18 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
-        <v>154</v>
+      <c r="A56" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2681,18 +2683,18 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
-        <v>157</v>
+      <c r="A57" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2700,18 +2702,18 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
-        <v>160</v>
+      <c r="A58" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2719,18 +2721,18 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
-        <v>163</v>
+      <c r="A59" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2738,18 +2740,18 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
-        <v>166</v>
+      <c r="A60" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2757,18 +2759,18 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="2" t="s">
-        <v>169</v>
+      <c r="A61" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2776,18 +2778,18 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
-        <v>172</v>
+      <c r="A62" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2795,18 +2797,18 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
-        <v>175</v>
+      <c r="A63" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2814,18 +2816,18 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2" t="s">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="2" t="s">
-        <v>178</v>
+      <c r="A64" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2833,18 +2835,18 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>180</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="2" t="s">
-        <v>181</v>
+      <c r="A65" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2852,18 +2854,18 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>183</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="2" t="s">
-        <v>184</v>
+      <c r="A66" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2871,18 +2873,18 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2" t="s">
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
-        <v>187</v>
+      <c r="A67" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2890,18 +2892,18 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
-        <v>190</v>
+      <c r="A68" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2909,18 +2911,18 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
-        <v>193</v>
+      <c r="A69" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2928,18 +2930,18 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2" t="s">
-        <v>194</v>
+        <v>127</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="2" t="s">
-        <v>196</v>
+      <c r="A70" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -2947,18 +2949,18 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2" t="s">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>198</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="2" t="s">
-        <v>199</v>
+      <c r="A71" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2966,18 +2968,18 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2" t="s">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>201</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="2" t="s">
-        <v>202</v>
+      <c r="A72" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -2985,18 +2987,18 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2" t="s">
-        <v>203</v>
+        <v>133</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>204</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="2" t="s">
-        <v>205</v>
+      <c r="A73" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3004,18 +3006,18 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="2" t="s">
-        <v>208</v>
+      <c r="A74" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3023,18 +3025,18 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2" t="s">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>210</v>
+        <v>138</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="2" t="s">
-        <v>211</v>
+      <c r="A75" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3042,18 +3044,18 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2" t="s">
-        <v>212</v>
+        <v>139</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>213</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="2" t="s">
-        <v>214</v>
+      <c r="A76" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3061,18 +3063,18 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>216</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="2" t="s">
-        <v>217</v>
+      <c r="A77" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3080,18 +3082,18 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2" t="s">
-        <v>218</v>
+        <v>143</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="2" t="s">
-        <v>220</v>
+      <c r="A78" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3099,18 +3101,18 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2" t="s">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>222</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="2" t="s">
-        <v>223</v>
+      <c r="A79" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3118,18 +3120,18 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="2" t="s">
-        <v>226</v>
+      <c r="A80" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3137,18 +3139,18 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2" t="s">
-        <v>227</v>
+        <v>149</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="2" t="s">
-        <v>229</v>
+      <c r="A81" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3156,18 +3158,18 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="2" t="s">
-        <v>232</v>
+      <c r="A82" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3175,18 +3177,18 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2" t="s">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="2" t="s">
-        <v>235</v>
+      <c r="A83" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3194,18 +3196,18 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>237</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="2" t="s">
-        <v>238</v>
+      <c r="A84" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3213,18 +3215,18 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2" t="s">
-        <v>239</v>
+        <v>157</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="2" t="s">
-        <v>241</v>
+      <c r="A85" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3232,18 +3234,18 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2" t="s">
-        <v>242</v>
+        <v>159</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="2" t="s">
-        <v>244</v>
+      <c r="A86" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3251,18 +3253,18 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2" t="s">
-        <v>245</v>
+        <v>161</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="2" t="s">
-        <v>247</v>
+      <c r="A87" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -3270,18 +3272,18 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2" t="s">
-        <v>248</v>
+        <v>163</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>249</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="2" t="s">
-        <v>250</v>
+      <c r="A88" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3289,18 +3291,18 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2" t="s">
-        <v>251</v>
+        <v>165</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>252</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="2" t="s">
-        <v>253</v>
+      <c r="A89" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -3308,18 +3310,18 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2" t="s">
-        <v>254</v>
+        <v>167</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="2" t="s">
-        <v>256</v>
+      <c r="A90" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -3327,18 +3329,18 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2" t="s">
-        <v>257</v>
+        <v>169</v>
       </c>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>258</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="2" t="s">
-        <v>259</v>
+      <c r="A91" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -3346,18 +3348,18 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2" t="s">
-        <v>260</v>
+        <v>171</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>261</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="2" t="s">
-        <v>262</v>
+      <c r="A92" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -3365,18 +3367,18 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2" t="s">
-        <v>263</v>
+        <v>173</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>264</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="2" t="s">
-        <v>265</v>
+      <c r="A93" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -3384,18 +3386,18 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2" t="s">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>267</v>
+        <v>176</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="2" t="s">
-        <v>268</v>
+      <c r="A94" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -3403,18 +3405,18 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="2" t="s">
-        <v>271</v>
+      <c r="A95" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -3422,18 +3424,18 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2" t="s">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>273</v>
+        <v>180</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="2" t="s">
-        <v>274</v>
+      <c r="A96" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -3441,18 +3443,18 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2" t="s">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>276</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="2" t="s">
-        <v>277</v>
+      <c r="A97" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -3460,18 +3462,18 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2" t="s">
-        <v>278</v>
+        <v>183</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
-        <v>279</v>
+        <v>184</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="2" t="s">
-        <v>280</v>
+      <c r="A98" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -3479,18 +3481,18 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>282</v>
+        <v>186</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="2" t="s">
-        <v>283</v>
+      <c r="A99" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -3498,18 +3500,18 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2" t="s">
-        <v>284</v>
+        <v>187</v>
       </c>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>285</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="2" t="s">
-        <v>286</v>
+      <c r="A100" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -3517,18 +3519,18 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
-        <v>288</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="2" t="s">
-        <v>289</v>
+      <c r="A101" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -3536,18 +3538,18 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2" t="s">
-        <v>290</v>
+        <v>191</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
-        <v>291</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="2" t="s">
-        <v>292</v>
+      <c r="A102" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -3555,18 +3557,18 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2" t="s">
-        <v>293</v>
+        <v>193</v>
       </c>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="2" t="s">
-        <v>295</v>
+      <c r="A103" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -3574,18 +3576,18 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2" t="s">
-        <v>296</v>
+        <v>195</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
-        <v>297</v>
+        <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="2" t="s">
-        <v>298</v>
+      <c r="A104" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -3593,18 +3595,18 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
-        <v>300</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="2" t="s">
-        <v>301</v>
+      <c r="A105" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -3612,18 +3614,18 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2" t="s">
-        <v>302</v>
+        <v>199</v>
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
-        <v>303</v>
+        <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="2" t="s">
-        <v>304</v>
+      <c r="A106" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -3631,18 +3633,18 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2" t="s">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2" t="s">
-        <v>306</v>
+        <v>202</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="2" t="s">
-        <v>307</v>
+      <c r="A107" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -3650,18 +3652,18 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2" t="s">
-        <v>308</v>
+        <v>203</v>
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
-        <v>309</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="2" t="s">
-        <v>310</v>
+      <c r="A108" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -3669,18 +3671,18 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2" t="s">
-        <v>311</v>
+        <v>205</v>
       </c>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
       <c r="K108" s="2" t="s">
-        <v>312</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="2" t="s">
-        <v>313</v>
+      <c r="A109" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -3688,18 +3690,18 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2" t="s">
-        <v>314</v>
+        <v>207</v>
       </c>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
-        <v>315</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="2" t="s">
-        <v>316</v>
+      <c r="A110" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -3707,18 +3709,18 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2" t="s">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="2" t="s">
-        <v>319</v>
+      <c r="A111" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -3726,18 +3728,18 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2" t="s">
-        <v>320</v>
+        <v>211</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="2" t="s">
-        <v>322</v>
+      <c r="A112" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -3745,18 +3747,18 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2" t="s">
-        <v>323</v>
+        <v>213</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
-        <v>324</v>
+        <v>214</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="2" t="s">
-        <v>325</v>
+      <c r="A113" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -3764,18 +3766,18 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2" t="s">
-        <v>326</v>
+        <v>215</v>
       </c>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
       <c r="K113" s="2" t="s">
-        <v>327</v>
+        <v>216</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="2" t="s">
-        <v>328</v>
+      <c r="A114" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -3783,18 +3785,18 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2" t="s">
-        <v>329</v>
+        <v>217</v>
       </c>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
-        <v>330</v>
+        <v>218</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="2" t="s">
-        <v>331</v>
+      <c r="A115" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -3802,18 +3804,18 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2" t="s">
-        <v>332</v>
+        <v>219</v>
       </c>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
-        <v>333</v>
+        <v>220</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="2" t="s">
-        <v>334</v>
+      <c r="A116" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -3821,18 +3823,18 @@
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2" t="s">
-        <v>335</v>
+        <v>221</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
-        <v>336</v>
+        <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="2" t="s">
-        <v>337</v>
+      <c r="A117" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -3840,18 +3842,18 @@
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2" t="s">
-        <v>338</v>
+        <v>223</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
       <c r="K117" s="2" t="s">
-        <v>339</v>
+        <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="2" t="s">
-        <v>340</v>
+      <c r="A118" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -3859,18 +3861,18 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2" t="s">
-        <v>341</v>
+        <v>225</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
       <c r="K118" s="2" t="s">
-        <v>342</v>
+        <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="2" t="s">
-        <v>343</v>
+      <c r="A119" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -3878,18 +3880,18 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2" t="s">
-        <v>344</v>
+        <v>227</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
       <c r="K119" s="2" t="s">
-        <v>345</v>
+        <v>228</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="2" t="s">
-        <v>346</v>
+      <c r="A120" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -3897,18 +3899,18 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2" t="s">
-        <v>347</v>
+        <v>229</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
       <c r="K120" s="2" t="s">
-        <v>348</v>
+        <v>230</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="2" t="s">
-        <v>349</v>
+      <c r="A121" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -3916,18 +3918,18 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2" t="s">
-        <v>350</v>
+        <v>231</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
       <c r="K121" s="2" t="s">
-        <v>351</v>
+        <v>232</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="2" t="s">
-        <v>352</v>
+      <c r="A122" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -3935,21 +3937,15 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2" t="s">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
       <c r="K122" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:11" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="125" spans="1:11" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="126" spans="1:11" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="127" spans="1:11" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:11" ht="15.5" x14ac:dyDescent="0.35"/>
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
